--- a/assignments/lab5/UserStory.xlsx
+++ b/assignments/lab5/UserStory.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29725"/>
   <workbookPr showInkAnnotation="0" autoCompressPictures="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu\home\sachxna\2sem\swe\swe-lab\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu\home\sachxna\2sem\swe\swe-lab\assignments\lab5\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{20319C80-7BDB-4406-AC22-8ECA2FFA98E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4817E675-12DF-4724-B6D6-D65735520A27}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="5">
   <si>
     <r>
       <rPr>
@@ -89,82 +89,7 @@
     </r>
   </si>
   <si>
-    <t>Faculty</t>
-  </si>
-  <si>
-    <t>Trigger Analytics and Generate Results</t>
-  </si>
-  <si>
-    <t>Update my Course Plan and Take Remedial Action.</t>
-  </si>
-  <si>
-    <t>Student</t>
-  </si>
-  <si>
-    <t>Upload Course Plan</t>
-  </si>
-  <si>
-    <t>So that students can access structured material.</t>
-  </si>
-  <si>
-    <t>Analyse student performance.</t>
-  </si>
-  <si>
-    <t>View topic-wise student performance</t>
-  </si>
-  <si>
-    <t>Identify the learning gaps in students.</t>
-  </si>
-  <si>
-    <t>Plan remedial action based on insight</t>
-  </si>
-  <si>
-    <t>Improve  students understanding in topics.</t>
-  </si>
-  <si>
-    <t>Communicate with students</t>
-  </si>
-  <si>
-    <t>Guide them or clarify doubts.</t>
-  </si>
-  <si>
-    <t>Follow the syllabus.</t>
-  </si>
-  <si>
-    <t>View datewise uploaded course material</t>
-  </si>
-  <si>
-    <t>View my attendance and performance</t>
-  </si>
-  <si>
-    <t>Identify my learning gaps.</t>
-  </si>
-  <si>
-    <t>Receive personalised remedial action</t>
-  </si>
-  <si>
-    <t>Communicate with faculty</t>
-  </si>
-  <si>
-    <t>Ask questions to gain clarity.</t>
-  </si>
-  <si>
-    <t>know my weak points in the subject.</t>
-  </si>
-  <si>
     <t>Priority</t>
-  </si>
-  <si>
-    <t>High</t>
-  </si>
-  <si>
-    <t>Low</t>
-  </si>
-  <si>
-    <t>Medium</t>
-  </si>
-  <si>
-    <t>Upload Student Information (attendance, answer scripts, question papers)</t>
   </si>
 </sst>
 </file>
@@ -615,178 +540,78 @@
         <v>1</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" ht="21.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="1">
-        <v>1</v>
-      </c>
-      <c r="B2" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="C2" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>26</v>
-      </c>
+    </row>
+    <row r="2" spans="1:5" ht="21.9" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="1"/>
+      <c r="B2" s="1"/>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1"/>
+      <c r="E2" s="1"/>
     </row>
     <row r="3" spans="1:5" ht="21.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="1">
-        <v>2</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>26</v>
-      </c>
+      <c r="A3" s="1"/>
+      <c r="B3" s="1"/>
+      <c r="C3" s="1"/>
+      <c r="D3" s="1"/>
+      <c r="E3" s="1"/>
     </row>
     <row r="4" spans="1:5" ht="21.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="1">
-        <v>3</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>26</v>
-      </c>
+      <c r="A4" s="1"/>
+      <c r="B4" s="1"/>
+      <c r="C4" s="1"/>
+      <c r="D4" s="1"/>
+      <c r="E4" s="1"/>
     </row>
     <row r="5" spans="1:5" ht="21.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="1">
-        <v>4</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="E5" s="1" t="s">
-        <v>28</v>
-      </c>
+      <c r="A5" s="1"/>
+      <c r="B5" s="1"/>
+      <c r="C5" s="1"/>
+      <c r="D5" s="1"/>
+      <c r="E5" s="1"/>
     </row>
     <row r="6" spans="1:5" ht="21.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="1">
-        <v>5</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="E6" s="1" t="s">
-        <v>28</v>
-      </c>
+      <c r="A6" s="1"/>
+      <c r="B6" s="1"/>
+      <c r="C6" s="1"/>
+      <c r="D6" s="1"/>
+      <c r="E6" s="1"/>
     </row>
     <row r="7" spans="1:5" ht="21.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="1">
-        <v>8</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="E7" s="1" t="s">
-        <v>28</v>
-      </c>
+      <c r="A7" s="1"/>
+      <c r="B7" s="1"/>
+      <c r="C7" s="1"/>
+      <c r="D7" s="1"/>
+      <c r="E7" s="1"/>
     </row>
     <row r="8" spans="1:5" ht="21.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="1">
-        <v>9</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="D8" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="E8" s="1" t="s">
-        <v>28</v>
-      </c>
+      <c r="A8" s="1"/>
+      <c r="B8" s="1"/>
+      <c r="C8" s="1"/>
+      <c r="D8" s="1"/>
+      <c r="E8" s="1"/>
     </row>
     <row r="9" spans="1:5" ht="21.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="1">
-        <v>6</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="D9" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="E9" s="1" t="s">
-        <v>27</v>
-      </c>
+      <c r="A9" s="1"/>
+      <c r="B9" s="1"/>
+      <c r="C9" s="1"/>
+      <c r="D9" s="1"/>
+      <c r="E9" s="1"/>
     </row>
     <row r="10" spans="1:5" ht="21.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="1">
-        <v>7</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C10" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="D10" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="E10" s="1" t="s">
-        <v>27</v>
-      </c>
+      <c r="A10" s="1"/>
+      <c r="B10" s="1"/>
+      <c r="C10" s="1"/>
+      <c r="D10" s="1"/>
+      <c r="E10" s="1"/>
     </row>
     <row r="11" spans="1:5" ht="21.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="1">
-        <v>10</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C11" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="D11" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="E11" s="1" t="s">
-        <v>27</v>
-      </c>
+      <c r="A11" s="1"/>
+      <c r="B11" s="1"/>
+      <c r="C11" s="1"/>
+      <c r="D11" s="1"/>
+      <c r="E11" s="1"/>
     </row>
     <row r="12" spans="1:5" ht="21.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="1"/>
